--- a/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Nhập kho/Tháng 10/NKSX_VNSH03-(SL-53)_171026.xlsx
+++ b/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Nhập kho/Tháng 10/NKSX_VNSH03-(SL-53)_171026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\2. Báo cáo - giấy tờ\3. Sản xuất\Xuất Nhập Kho 2026\Nhập kho\Tháng 10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D0EB48A-4403-40F2-BBF2-529CE34B9068}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAC607BF-8ABB-4133-8A9E-E422C9C5BF3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Nhập kho/Tháng 10/NKSX_VNSH03-(SL-53)_171026.xlsx
+++ b/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Nhập kho/Tháng 10/NKSX_VNSH03-(SL-53)_171026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\2. Báo cáo - giấy tờ\3. Sản xuất\Xuất Nhập Kho 2026\Nhập kho\Tháng 10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAC607BF-8ABB-4133-8A9E-E422C9C5BF3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B410D2B-A3E3-49A5-AAAE-EE9EC49CDE6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NhapKho_SX" sheetId="10" r:id="rId1"/>
@@ -1563,7 +1563,7 @@
         <v>24</v>
       </c>
       <c r="D9" s="33">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="32"/>
